--- a/ResourcesPK/UserBulkUpload.xlsx
+++ b/ResourcesPK/UserBulkUpload.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="169">
   <si>
     <t>Code*</t>
   </si>
@@ -448,6 +448,84 @@
   </si>
   <si>
     <t>66257-8143620-0</t>
+  </si>
+  <si>
+    <t>User_87143</t>
+  </si>
+  <si>
+    <t>Auto_22853</t>
+  </si>
+  <si>
+    <t>42894-3497980-0</t>
+  </si>
+  <si>
+    <t>User_1CF4B</t>
+  </si>
+  <si>
+    <t>Auto_DF9BB</t>
+  </si>
+  <si>
+    <t>42894-3548180-0</t>
+  </si>
+  <si>
+    <t>User_58BB4</t>
+  </si>
+  <si>
+    <t>Auto_7041F</t>
+  </si>
+  <si>
+    <t>7439275283000</t>
+  </si>
+  <si>
+    <t>User_13F8E</t>
+  </si>
+  <si>
+    <t>Auto_5D861</t>
+  </si>
+  <si>
+    <t>7439275942200</t>
+  </si>
+  <si>
+    <t>User_7998E</t>
+  </si>
+  <si>
+    <t>Auto_352FF</t>
+  </si>
+  <si>
+    <t>04619-7516380-0</t>
+  </si>
+  <si>
+    <t>0461975163800</t>
+  </si>
+  <si>
+    <t>User_618E4</t>
+  </si>
+  <si>
+    <t>Auto_EDD4C</t>
+  </si>
+  <si>
+    <t>04619-7743510-0</t>
+  </si>
+  <si>
+    <t>0461977435100</t>
+  </si>
+  <si>
+    <t>User_D4E3B</t>
+  </si>
+  <si>
+    <t>Auto_34006</t>
+  </si>
+  <si>
+    <t>06034-7519400-0</t>
+  </si>
+  <si>
+    <t>User_5BC8D</t>
+  </si>
+  <si>
+    <t>Auto_55AD4</t>
+  </si>
+  <si>
+    <t>06034-7710330-0</t>
   </si>
 </sst>
 </file>
@@ -843,13 +921,13 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>15</v>
@@ -890,13 +968,13 @@
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>

--- a/ResourcesPK/UserBulkUpload.xlsx
+++ b/ResourcesPK/UserBulkUpload.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Huzaifa\JAR\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" concurrentManualCount="8"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="103">
   <si>
     <t>Code*</t>
   </si>
@@ -81,12 +81,6 @@
     <t>D</t>
   </si>
   <si>
-    <t>Temp User11</t>
-  </si>
-  <si>
-    <t>Temp User12</t>
-  </si>
-  <si>
     <t>0002</t>
   </si>
   <si>
@@ -96,436 +90,244 @@
     <t>ur</t>
   </si>
   <si>
-    <t>12345-0123456-1</t>
-  </si>
-  <si>
-    <t>12345-0123456-2</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>User_427CA</t>
-  </si>
-  <si>
-    <t>Auto_46B25</t>
-  </si>
-  <si>
-    <t>24681-5169100-0</t>
-  </si>
-  <si>
-    <t>User_11687</t>
-  </si>
-  <si>
-    <t>Auto_217A9</t>
-  </si>
-  <si>
-    <t>24681-6028530-0</t>
-  </si>
-  <si>
-    <t>User_99BE7</t>
-  </si>
-  <si>
-    <t>Auto_E6393</t>
-  </si>
-  <si>
-    <t>37717-0983180-0</t>
-  </si>
-  <si>
-    <t>User_E6594</t>
-  </si>
-  <si>
-    <t>Auto_40387</t>
-  </si>
-  <si>
-    <t>37717-1892560-0</t>
-  </si>
-  <si>
-    <t>User_C1FC8</t>
-  </si>
-  <si>
-    <t>Auto_D6B80</t>
-  </si>
-  <si>
-    <t>38710-9075540-0</t>
-  </si>
-  <si>
-    <t>User_DD9A1</t>
-  </si>
-  <si>
-    <t>Auto_6F750</t>
-  </si>
-  <si>
-    <t>38710-9910590-0</t>
-  </si>
-  <si>
-    <t>User_A0F5C</t>
-  </si>
-  <si>
-    <t>Auto_FF25A</t>
-  </si>
-  <si>
-    <t>63200-6844900-0</t>
-  </si>
-  <si>
-    <t>User_E4E58</t>
-  </si>
-  <si>
-    <t>Auto_3FEA8</t>
-  </si>
-  <si>
-    <t>63200-7792240-0</t>
-  </si>
-  <si>
-    <t>User_C5D6A</t>
-  </si>
-  <si>
-    <t>Auto_B9DE5</t>
-  </si>
-  <si>
-    <t>79926-8478770-0</t>
-  </si>
-  <si>
-    <t>User_DF6D0</t>
-  </si>
-  <si>
-    <t>Auto_0380B</t>
-  </si>
-  <si>
-    <t>79926-9319490-0</t>
-  </si>
-  <si>
-    <t>User_A2EC5</t>
-  </si>
-  <si>
-    <t>Auto_04DAD</t>
-  </si>
-  <si>
-    <t>37978-9615190-0</t>
-  </si>
-  <si>
-    <t>User_92DC5</t>
-  </si>
-  <si>
-    <t>Auto_63D5F</t>
-  </si>
-  <si>
-    <t>37979-0834620-0</t>
-  </si>
-  <si>
-    <t>User_F16B3</t>
-  </si>
-  <si>
-    <t>Auto_A112C</t>
-  </si>
-  <si>
-    <t>40693-3467530-0</t>
-  </si>
-  <si>
-    <t>User_E8B4F</t>
-  </si>
-  <si>
-    <t>Auto_68193</t>
-  </si>
-  <si>
-    <t>40693-4633520-0</t>
-  </si>
-  <si>
-    <t>User_1BC02</t>
-  </si>
-  <si>
-    <t>Auto_E4B19</t>
-  </si>
-  <si>
-    <t>55771-3331130-0</t>
-  </si>
-  <si>
-    <t>User_B68D1</t>
-  </si>
-  <si>
-    <t>Auto_A6AE3</t>
-  </si>
-  <si>
-    <t>55771-3465080-0</t>
-  </si>
-  <si>
-    <t>User_B2C32</t>
-  </si>
-  <si>
-    <t>Auto_AAE49</t>
-  </si>
-  <si>
-    <t>65577-1268450-0</t>
-  </si>
-  <si>
-    <t>User_52C8D</t>
-  </si>
-  <si>
-    <t>Auto_845A7</t>
-  </si>
-  <si>
-    <t>65577-1416670-0</t>
-  </si>
-  <si>
-    <t>User_095BA</t>
-  </si>
-  <si>
-    <t>Auto_11C06</t>
-  </si>
-  <si>
-    <t>86421-3925770-0</t>
-  </si>
-  <si>
-    <t>User_6CC0A</t>
-  </si>
-  <si>
-    <t>Auto_61F9E</t>
-  </si>
-  <si>
-    <t>86421-4045980-0</t>
-  </si>
-  <si>
-    <t>User_A0541</t>
-  </si>
-  <si>
-    <t>Auto_A85D6</t>
-  </si>
-  <si>
-    <t>30100-1100480-0</t>
-  </si>
-  <si>
-    <t>User_84B2C</t>
-  </si>
-  <si>
-    <t>Auto_2F814</t>
-  </si>
-  <si>
-    <t>30100-1228110-0</t>
-  </si>
-  <si>
-    <t>User_A7F88</t>
-  </si>
-  <si>
-    <t>Auto_07435</t>
-  </si>
-  <si>
-    <t>40203-4690270-0</t>
-  </si>
-  <si>
-    <t>User_9B987</t>
-  </si>
-  <si>
-    <t>Auto_86207</t>
-  </si>
-  <si>
-    <t>40203-5797200-0</t>
-  </si>
-  <si>
-    <t>User_3C53B</t>
-  </si>
-  <si>
-    <t>Auto_16408</t>
-  </si>
-  <si>
-    <t>20611-4998410-0</t>
-  </si>
-  <si>
-    <t>User_614C4</t>
-  </si>
-  <si>
-    <t>Auto_15C84</t>
-  </si>
-  <si>
-    <t>20611-5129740-0</t>
-  </si>
-  <si>
-    <t>User_B5723</t>
-  </si>
-  <si>
-    <t>Auto_A9433</t>
-  </si>
-  <si>
-    <t>33400-6739510-0</t>
-  </si>
-  <si>
-    <t>User_3173B</t>
-  </si>
-  <si>
-    <t>Auto_AB689</t>
-  </si>
-  <si>
-    <t>33400-6890870-0</t>
-  </si>
-  <si>
-    <t>User_53552</t>
-  </si>
-  <si>
-    <t>Auto_1E1FF</t>
-  </si>
-  <si>
-    <t>67153-5900510-0</t>
-  </si>
-  <si>
-    <t>User_83748</t>
-  </si>
-  <si>
-    <t>Auto_ED05A</t>
-  </si>
-  <si>
-    <t>67153-6028650-0</t>
-  </si>
-  <si>
-    <t>User_A5013</t>
-  </si>
-  <si>
-    <t>Auto_8F32A</t>
-  </si>
-  <si>
-    <t>03417-5072360-0</t>
-  </si>
-  <si>
-    <t>User_A9375</t>
-  </si>
-  <si>
-    <t>Auto_26FAD</t>
-  </si>
-  <si>
-    <t>03417-5453490-0</t>
-  </si>
-  <si>
-    <t>User_5196D</t>
-  </si>
-  <si>
-    <t>Auto_7F0C0</t>
-  </si>
-  <si>
-    <t>52736-3788660-0</t>
-  </si>
-  <si>
-    <t>User_55434</t>
-  </si>
-  <si>
-    <t>Auto_A369D</t>
-  </si>
-  <si>
-    <t>52736-3898430-0</t>
-  </si>
-  <si>
-    <t>User_851E4</t>
-  </si>
-  <si>
-    <t>Auto_35D53</t>
-  </si>
-  <si>
-    <t>80000-1218560-0</t>
-  </si>
-  <si>
-    <t>User_71E64</t>
-  </si>
-  <si>
-    <t>Auto_405A9</t>
-  </si>
-  <si>
-    <t>80000-1395300-0</t>
-  </si>
-  <si>
-    <t>User_E6CC2</t>
-  </si>
-  <si>
-    <t>Auto_A0857</t>
-  </si>
-  <si>
-    <t>66257-7907260-0</t>
-  </si>
-  <si>
-    <t>User_F9FB4</t>
-  </si>
-  <si>
-    <t>Auto_F305A</t>
-  </si>
-  <si>
-    <t>66257-8143620-0</t>
-  </si>
-  <si>
-    <t>User_87143</t>
-  </si>
-  <si>
-    <t>Auto_22853</t>
-  </si>
-  <si>
-    <t>42894-3497980-0</t>
-  </si>
-  <si>
-    <t>User_1CF4B</t>
-  </si>
-  <si>
-    <t>Auto_DF9BB</t>
-  </si>
-  <si>
-    <t>42894-3548180-0</t>
-  </si>
-  <si>
-    <t>User_58BB4</t>
-  </si>
-  <si>
-    <t>Auto_7041F</t>
-  </si>
-  <si>
-    <t>7439275283000</t>
-  </si>
-  <si>
-    <t>User_13F8E</t>
-  </si>
-  <si>
-    <t>Auto_5D861</t>
-  </si>
-  <si>
-    <t>7439275942200</t>
-  </si>
-  <si>
-    <t>User_7998E</t>
-  </si>
-  <si>
-    <t>Auto_352FF</t>
-  </si>
-  <si>
-    <t>04619-7516380-0</t>
-  </si>
-  <si>
-    <t>0461975163800</t>
-  </si>
-  <si>
-    <t>User_618E4</t>
-  </si>
-  <si>
-    <t>Auto_EDD4C</t>
-  </si>
-  <si>
-    <t>04619-7743510-0</t>
-  </si>
-  <si>
-    <t>0461977435100</t>
-  </si>
-  <si>
-    <t>User_D4E3B</t>
-  </si>
-  <si>
-    <t>Auto_34006</t>
-  </si>
-  <si>
-    <t>06034-7519400-0</t>
-  </si>
-  <si>
-    <t>User_5BC8D</t>
-  </si>
-  <si>
-    <t>Auto_55AD4</t>
-  </si>
-  <si>
-    <t>06034-7710330-0</t>
+    <t>User_6D98E</t>
+  </si>
+  <si>
+    <t>Auto_5F6EE</t>
+  </si>
+  <si>
+    <t>20451-0388810-0</t>
+  </si>
+  <si>
+    <t>User_CE860</t>
+  </si>
+  <si>
+    <t>Auto_773F8</t>
+  </si>
+  <si>
+    <t>20451-0435170-0</t>
+  </si>
+  <si>
+    <t>User_0327E</t>
+  </si>
+  <si>
+    <t>Auto_B2ABA</t>
+  </si>
+  <si>
+    <t>41070-5387720-0</t>
+  </si>
+  <si>
+    <t>User_4E335</t>
+  </si>
+  <si>
+    <t>Auto_DA817</t>
+  </si>
+  <si>
+    <t>41070-5444639-9</t>
+  </si>
+  <si>
+    <t>User_76B05</t>
+  </si>
+  <si>
+    <t>Auto_9511C</t>
+  </si>
+  <si>
+    <t>68144-8593070-0</t>
+  </si>
+  <si>
+    <t>User_2463B</t>
+  </si>
+  <si>
+    <t>Auto_480F0</t>
+  </si>
+  <si>
+    <t>68144-8638660-0</t>
+  </si>
+  <si>
+    <t>User_B142E</t>
+  </si>
+  <si>
+    <t>Auto_6AB3D</t>
+  </si>
+  <si>
+    <t>14077-4818190-0</t>
+  </si>
+  <si>
+    <t>User_09973</t>
+  </si>
+  <si>
+    <t>Auto_4C68C</t>
+  </si>
+  <si>
+    <t>14077-4893980-0</t>
+  </si>
+  <si>
+    <t>User_95B4B</t>
+  </si>
+  <si>
+    <t>Auto_08D4B</t>
+  </si>
+  <si>
+    <t>25520-4227350-0</t>
+  </si>
+  <si>
+    <t>User_F948E</t>
+  </si>
+  <si>
+    <t>Auto_48F80</t>
+  </si>
+  <si>
+    <t>25520-4290450-0</t>
+  </si>
+  <si>
+    <t>User_95828</t>
+  </si>
+  <si>
+    <t>Auto_F2DEE</t>
+  </si>
+  <si>
+    <t>37726-6646540-0</t>
+  </si>
+  <si>
+    <t>User_7E43F</t>
+  </si>
+  <si>
+    <t>Auto_10E08</t>
+  </si>
+  <si>
+    <t>37726-6713110-0</t>
+  </si>
+  <si>
+    <t>User_F4CFA</t>
+  </si>
+  <si>
+    <t>Auto_45847</t>
+  </si>
+  <si>
+    <t>69691-6983300-0</t>
+  </si>
+  <si>
+    <t>User_EA29C</t>
+  </si>
+  <si>
+    <t>Auto_F0444</t>
+  </si>
+  <si>
+    <t>69691-7042980-0</t>
+  </si>
+  <si>
+    <t>User_2680E</t>
+  </si>
+  <si>
+    <t>Auto_E7E87</t>
+  </si>
+  <si>
+    <t>97200-4200320-0</t>
+  </si>
+  <si>
+    <t>User_38B5E</t>
+  </si>
+  <si>
+    <t>Auto_C799C</t>
+  </si>
+  <si>
+    <t>97200-4272150-0</t>
+  </si>
+  <si>
+    <t>User_A1B59</t>
+  </si>
+  <si>
+    <t>Auto_AE793</t>
+  </si>
+  <si>
+    <t>29300-6123920-0</t>
+  </si>
+  <si>
+    <t>User_F0655</t>
+  </si>
+  <si>
+    <t>Auto_031D3</t>
+  </si>
+  <si>
+    <t>29300-6177520-0</t>
+  </si>
+  <si>
+    <t>User_6B0C8</t>
+  </si>
+  <si>
+    <t>Auto_0256A</t>
+  </si>
+  <si>
+    <t>37638-3384120-0</t>
+  </si>
+  <si>
+    <t>User_171BD</t>
+  </si>
+  <si>
+    <t>Auto_60EBD</t>
+  </si>
+  <si>
+    <t>37638-3438370-0</t>
+  </si>
+  <si>
+    <t>User_D0282</t>
+  </si>
+  <si>
+    <t>Auto_27F1A</t>
+  </si>
+  <si>
+    <t>46277-5928000-0</t>
+  </si>
+  <si>
+    <t>User_0CF6C</t>
+  </si>
+  <si>
+    <t>Auto_3C041</t>
+  </si>
+  <si>
+    <t>46277-6009430-0</t>
+  </si>
+  <si>
+    <t>User_AC0C7</t>
+  </si>
+  <si>
+    <t>Auto_48EB0</t>
+  </si>
+  <si>
+    <t>60740-1164720-0</t>
+  </si>
+  <si>
+    <t>User_1771A</t>
+  </si>
+  <si>
+    <t>Auto_EF504</t>
+  </si>
+  <si>
+    <t>60740-1245430-0</t>
+  </si>
+  <si>
+    <t>User_3191D</t>
+  </si>
+  <si>
+    <t>Auto_0F214</t>
+  </si>
+  <si>
+    <t>72442-1768430-0</t>
+  </si>
+  <si>
+    <t>User_94FD8</t>
+  </si>
+  <si>
+    <t>Auto_6D4C7</t>
+  </si>
+  <si>
+    <t>72442-1886100-0</t>
   </si>
 </sst>
 </file>
@@ -853,26 +655,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="14.6328125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="11.81640625"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="16.54296875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="10.453125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="7.453125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.26953125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="17.81640625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="25.1796875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="8.54296875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="10.54296875"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="22.81640625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="13.453125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="17.26953125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="10.1796875"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="16.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="10.42578125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="7.42578125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.28515625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="17.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="25.140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="8.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="10.5703125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="22.85546875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="13.42578125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="17.28515625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="10.140625"/>
     <col min="15" max="15" bestFit="true" customWidth="true" width="6.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
@@ -919,15 +721,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>15</v>
@@ -939,7 +741,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H2" s="0">
         <v>99</v>
@@ -951,30 +753,30 @@
         <v>9</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
@@ -983,7 +785,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>17</v>
@@ -998,19 +800,19 @@
         <v>9</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/ResourcesPK/UserBulkUpload.xlsx
+++ b/ResourcesPK/UserBulkUpload.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="133">
   <si>
     <t>Code*</t>
   </si>
@@ -328,6 +328,96 @@
   </si>
   <si>
     <t>72442-1886100-0</t>
+  </si>
+  <si>
+    <t>User_83C45</t>
+  </si>
+  <si>
+    <t>Auto_48DD0</t>
+  </si>
+  <si>
+    <t>97380-7544590-0</t>
+  </si>
+  <si>
+    <t>User_A1E1E</t>
+  </si>
+  <si>
+    <t>Auto_27A7B</t>
+  </si>
+  <si>
+    <t>97380-7616640-0</t>
+  </si>
+  <si>
+    <t>User_21E5F</t>
+  </si>
+  <si>
+    <t>Auto_A3F83</t>
+  </si>
+  <si>
+    <t>84072-8328180-0</t>
+  </si>
+  <si>
+    <t>User_BA12A</t>
+  </si>
+  <si>
+    <t>Auto_7F419</t>
+  </si>
+  <si>
+    <t>84072-8370040-0</t>
+  </si>
+  <si>
+    <t>User_36161</t>
+  </si>
+  <si>
+    <t>Auto_1D677</t>
+  </si>
+  <si>
+    <t>72184-5523840-0</t>
+  </si>
+  <si>
+    <t>User_26B04</t>
+  </si>
+  <si>
+    <t>Auto_044D1</t>
+  </si>
+  <si>
+    <t>72184-5582500-0</t>
+  </si>
+  <si>
+    <t>User_0DCD9</t>
+  </si>
+  <si>
+    <t>Auto_FCBFC</t>
+  </si>
+  <si>
+    <t>81823-4669580-0</t>
+  </si>
+  <si>
+    <t>User_C99E7</t>
+  </si>
+  <si>
+    <t>Auto_C6BD0</t>
+  </si>
+  <si>
+    <t>81823-4728340-0</t>
+  </si>
+  <si>
+    <t>User_61ECB</t>
+  </si>
+  <si>
+    <t>Auto_49966</t>
+  </si>
+  <si>
+    <t>98262-3843310-0</t>
+  </si>
+  <si>
+    <t>User_14B97</t>
+  </si>
+  <si>
+    <t>Auto_68DFB</t>
+  </si>
+  <si>
+    <t>98262-3902510-0</t>
   </si>
 </sst>
 </file>
@@ -723,13 +813,13 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>15</v>
@@ -770,13 +860,13 @@
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>

--- a/ResourcesPK/UserBulkUpload.xlsx
+++ b/ResourcesPK/UserBulkUpload.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="241">
   <si>
     <t>Code*</t>
   </si>
@@ -418,6 +418,330 @@
   </si>
   <si>
     <t>98262-3902510-0</t>
+  </si>
+  <si>
+    <t>User_B6BE7</t>
+  </si>
+  <si>
+    <t>Auto_299E4</t>
+  </si>
+  <si>
+    <t>72035-6781340-0</t>
+  </si>
+  <si>
+    <t>User_64728</t>
+  </si>
+  <si>
+    <t>Auto_2189A</t>
+  </si>
+  <si>
+    <t>72035-6866230-0</t>
+  </si>
+  <si>
+    <t>User_8F71D</t>
+  </si>
+  <si>
+    <t>Auto_852A6</t>
+  </si>
+  <si>
+    <t>78107-5361130-0</t>
+  </si>
+  <si>
+    <t>User_31611</t>
+  </si>
+  <si>
+    <t>Auto_9538C</t>
+  </si>
+  <si>
+    <t>78107-5433670-0</t>
+  </si>
+  <si>
+    <t>User_AD2E8</t>
+  </si>
+  <si>
+    <t>Auto_E6B24</t>
+  </si>
+  <si>
+    <t>80422-4578830-0</t>
+  </si>
+  <si>
+    <t>User_522E1</t>
+  </si>
+  <si>
+    <t>Auto_61748</t>
+  </si>
+  <si>
+    <t>80422-4630690-0</t>
+  </si>
+  <si>
+    <t>User_BEA32</t>
+  </si>
+  <si>
+    <t>Auto_A7ECC</t>
+  </si>
+  <si>
+    <t>02784-5881110-0</t>
+  </si>
+  <si>
+    <t>User_F08A3</t>
+  </si>
+  <si>
+    <t>Auto_B8A81</t>
+  </si>
+  <si>
+    <t>02784-5949310-0</t>
+  </si>
+  <si>
+    <t>User_67C47</t>
+  </si>
+  <si>
+    <t>Auto_C5912</t>
+  </si>
+  <si>
+    <t>04791-1137120-0</t>
+  </si>
+  <si>
+    <t>User_AD9A9</t>
+  </si>
+  <si>
+    <t>Auto_22F9E</t>
+  </si>
+  <si>
+    <t>04791-1329480-0</t>
+  </si>
+  <si>
+    <t>User_D222A</t>
+  </si>
+  <si>
+    <t>Auto_CCF01</t>
+  </si>
+  <si>
+    <t>07809-5130600-0</t>
+  </si>
+  <si>
+    <t>User_E2C74</t>
+  </si>
+  <si>
+    <t>Auto_79E96</t>
+  </si>
+  <si>
+    <t>07809-5224710-0</t>
+  </si>
+  <si>
+    <t>User_166E2</t>
+  </si>
+  <si>
+    <t>Auto_B0961</t>
+  </si>
+  <si>
+    <t>20946-3510140-0</t>
+  </si>
+  <si>
+    <t>User_CB599</t>
+  </si>
+  <si>
+    <t>Auto_34C32</t>
+  </si>
+  <si>
+    <t>20946-3631240-0</t>
+  </si>
+  <si>
+    <t>User_E8B38</t>
+  </si>
+  <si>
+    <t>Auto_23798</t>
+  </si>
+  <si>
+    <t>63864-3660280-0</t>
+  </si>
+  <si>
+    <t>User_6E15E</t>
+  </si>
+  <si>
+    <t>Auto_5D752</t>
+  </si>
+  <si>
+    <t>63864-3708450-0</t>
+  </si>
+  <si>
+    <t>User_F080C</t>
+  </si>
+  <si>
+    <t>Auto_B7955</t>
+  </si>
+  <si>
+    <t>90689-8246400-0</t>
+  </si>
+  <si>
+    <t>User_E4B02</t>
+  </si>
+  <si>
+    <t>Auto_CDF11</t>
+  </si>
+  <si>
+    <t>90689-8279830-0</t>
+  </si>
+  <si>
+    <t>User_EA048</t>
+  </si>
+  <si>
+    <t>Auto_58E44</t>
+  </si>
+  <si>
+    <t>84996-1875340-0</t>
+  </si>
+  <si>
+    <t>User_FCC97</t>
+  </si>
+  <si>
+    <t>Auto_A7AEB</t>
+  </si>
+  <si>
+    <t>84996-1938370-0</t>
+  </si>
+  <si>
+    <t>User_21622</t>
+  </si>
+  <si>
+    <t>Auto_1C819</t>
+  </si>
+  <si>
+    <t>22508-8426640-0</t>
+  </si>
+  <si>
+    <t>User_C1291</t>
+  </si>
+  <si>
+    <t>Auto_779A3</t>
+  </si>
+  <si>
+    <t>22508-8465100-0</t>
+  </si>
+  <si>
+    <t>User_633B2</t>
+  </si>
+  <si>
+    <t>Auto_88B60</t>
+  </si>
+  <si>
+    <t>34138-0706620-0</t>
+  </si>
+  <si>
+    <t>User_14D41</t>
+  </si>
+  <si>
+    <t>Auto_83DF9</t>
+  </si>
+  <si>
+    <t>34138-0778320-0</t>
+  </si>
+  <si>
+    <t>User_57A4B</t>
+  </si>
+  <si>
+    <t>Auto_AAB08</t>
+  </si>
+  <si>
+    <t>02816-1125540-0</t>
+  </si>
+  <si>
+    <t>User_D71E3</t>
+  </si>
+  <si>
+    <t>Auto_18E6F</t>
+  </si>
+  <si>
+    <t>02816-1159040-0</t>
+  </si>
+  <si>
+    <t>User_8F563</t>
+  </si>
+  <si>
+    <t>Auto_2E9E8</t>
+  </si>
+  <si>
+    <t>79729-8456090-0</t>
+  </si>
+  <si>
+    <t>User_FCA9D</t>
+  </si>
+  <si>
+    <t>Auto_FA8F5</t>
+  </si>
+  <si>
+    <t>79729-8492720-0</t>
+  </si>
+  <si>
+    <t>User_1F357</t>
+  </si>
+  <si>
+    <t>Auto_8B07D</t>
+  </si>
+  <si>
+    <t>37301-7777710-0</t>
+  </si>
+  <si>
+    <t>User_563D7</t>
+  </si>
+  <si>
+    <t>Auto_CCF14</t>
+  </si>
+  <si>
+    <t>37301-7870520-0</t>
+  </si>
+  <si>
+    <t>User_DA103</t>
+  </si>
+  <si>
+    <t>Auto_FEFB3</t>
+  </si>
+  <si>
+    <t>62949-9672110-0</t>
+  </si>
+  <si>
+    <t>User_F2054</t>
+  </si>
+  <si>
+    <t>Auto_697D1</t>
+  </si>
+  <si>
+    <t>62949-9772300-0</t>
+  </si>
+  <si>
+    <t>User_07868</t>
+  </si>
+  <si>
+    <t>Auto_18214</t>
+  </si>
+  <si>
+    <t>72026-1106100-0</t>
+  </si>
+  <si>
+    <t>User_3F987</t>
+  </si>
+  <si>
+    <t>Auto_47169</t>
+  </si>
+  <si>
+    <t>72026-1139760-0</t>
+  </si>
+  <si>
+    <t>User_53626</t>
+  </si>
+  <si>
+    <t>Auto_E440A</t>
+  </si>
+  <si>
+    <t>64771-0687750-0</t>
+  </si>
+  <si>
+    <t>User_D1439</t>
+  </si>
+  <si>
+    <t>Auto_0B09A</t>
+  </si>
+  <si>
+    <t>64771-0745180-0</t>
   </si>
 </sst>
 </file>
@@ -813,13 +1137,13 @@
     </row>
     <row r="2" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>127</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>129</v>
+        <v>237</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>15</v>
@@ -860,13 +1184,13 @@
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s" s="0">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>131</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>15</v>
